--- a/Assignment 1 - Test cases.xlsx
+++ b/Assignment 1 - Test cases.xlsx
@@ -543,7 +543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="49.95" customHeight="1"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -552,8 +552,8 @@
     <col width="48" customWidth="1" min="4" max="4"/>
     <col width="48" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="14.33203125" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
     <col width="12.33203125" customWidth="1" min="9" max="10"/>
   </cols>
   <sheetData>
@@ -588,8 +588,18 @@
           <t>Status</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="50" customHeight="1">
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>Singlish input types covered</t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t>Evidence or rationale for the input type covered</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="55" customHeight="1">
       <c r="A2" s="10" t="inlineStr">
         <is>
           <t>Neg_0001</t>
@@ -620,8 +630,18 @@
           <t>Fail</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="50" customHeight="1">
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>Question forms</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>Rationale: The overall message is a question asking 'how are you' in Singlish form.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="55" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Neg_0002</t>
@@ -652,8 +672,18 @@
           <t>Fail</t>
         </is>
       </c>
-    </row>
-    <row r="4" ht="50" customHeight="1">
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>Question forms</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>Evidence: "oya kavadhdha aave?" — The sentence is a question asking when someone came.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="55" customHeight="1">
       <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Neg_0003</t>
@@ -684,8 +714,18 @@
           <t>Fail</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="50" customHeight="1">
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>Command forms</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>Rationale: "vahaama enna" is an imperative command meaning 'come quickly', directed at 'machan' (friend).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="55" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Neg_0004</t>
@@ -716,8 +756,18 @@
           <t>Fail</t>
         </is>
       </c>
-    </row>
-    <row r="6" ht="50" customHeight="1">
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>Command forms</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>Rationale: "denna" is a command form meaning 'give me', making the sentence an imperative request.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="55" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Neg_0005</t>
@@ -748,8 +798,18 @@
           <t>Fail</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="50" customHeight="1">
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>Greetings</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>Rationale: "suba udhaeesanak" is a Singlish greeting meaning 'good morning'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="55" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Neg_0006</t>
@@ -780,8 +840,18 @@
           <t>Fail</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="50" customHeight="1">
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>Greetings</t>
+        </is>
+      </c>
+      <c r="H7" s="12" t="inlineStr">
+        <is>
+          <t>Rationale: "aayuboovan" is a traditional Sinhala greeting meaning 'may you live long'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="55" customHeight="1">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Neg_0007</t>
@@ -812,8 +882,18 @@
           <t>Fail</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="50" customHeight="1">
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>Requests</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>Rationale: "puLuvan naedha" is a polite request form asking if someone is able to come home.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="55" customHeight="1">
       <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Neg_0008</t>
@@ -844,8 +924,18 @@
           <t>Fail</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="50" customHeight="1">
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>Requests</t>
+        </is>
+      </c>
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <t>Rationale: "evanna puLuvan" is a request form asking if someone is able to send something.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="55" customHeight="1">
       <c r="A10" s="10" t="inlineStr">
         <is>
           <t>Neg_0009</t>
@@ -876,8 +966,18 @@
           <t>Fail</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="50" customHeight="1">
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>Responses</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>Rationale: "hari" is an affirmative response meaning 'okay/yes', followed by a commitment statement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="55" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
           <t>Neg_0010</t>
@@ -908,8 +1008,18 @@
           <t>Fail</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="50" customHeight="1">
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>Responses</t>
+        </is>
+      </c>
+      <c r="H11" s="12" t="inlineStr">
+        <is>
+          <t>Rationale: "naee" and "baee" are negative response forms meaning 'no' and 'can't'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="55" customHeight="1">
       <c r="A12" s="10" t="inlineStr">
         <is>
           <t>Neg_0011</t>
@@ -940,8 +1050,18 @@
           <t>Fail</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="50" customHeight="1">
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>Repeated Words</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>Rationale: "hari hari" is a repeated word used for emphasis meaning 'okay okay'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="55" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
         <is>
           <t>Neg_0012</t>
@@ -972,8 +1092,18 @@
           <t>Fail</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="50" customHeight="1">
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>Repeated Words</t>
+        </is>
+      </c>
+      <c r="H13" s="12" t="inlineStr">
+        <is>
+          <t>Rationale: "tika tika" is a repeated word meaning 'little by little', used for emphasis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="55" customHeight="1">
       <c r="A14" s="10" t="inlineStr">
         <is>
           <t>Neg_0013</t>
@@ -1004,8 +1134,18 @@
           <t>Fail</t>
         </is>
       </c>
-    </row>
-    <row r="15" ht="50" customHeight="1">
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>Inputs with Punctuation Marks</t>
+        </is>
+      </c>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>Rationale: The input uses an ellipsis "…" and a question mark "?" as punctuation marks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="55" customHeight="1">
       <c r="A15" s="12" t="inlineStr">
         <is>
           <t>Neg_0014</t>
@@ -1036,8 +1176,18 @@
           <t>Fail</t>
         </is>
       </c>
-    </row>
-    <row r="16" ht="50" customHeight="1">
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>Inputs with Punctuation Marks</t>
+        </is>
+      </c>
+      <c r="H15" s="12" t="inlineStr">
+        <is>
+          <t>Rationale: The input uses an exclamation mark "!" and a full stop "." as punctuation marks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="55" customHeight="1">
       <c r="A16" s="10" t="inlineStr">
         <is>
           <t>Neg_0015</t>
@@ -1068,8 +1218,18 @@
           <t>Fail</t>
         </is>
       </c>
-    </row>
-    <row r="17" ht="50" customHeight="1">
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>Romanization / Spelling Variants</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>Rationale: The word 'ආදරෙයි' is written as 'adrei' which is a shortened spelling variant of 'adareyi'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="55" customHeight="1">
       <c r="A17" s="12" t="inlineStr">
         <is>
           <t>Neg_0016</t>
@@ -1100,8 +1260,18 @@
           <t>Fail</t>
         </is>
       </c>
-    </row>
-    <row r="18" ht="50" customHeight="1">
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>Romanization / Spelling Variants</t>
+        </is>
+      </c>
+      <c r="H17" s="12" t="inlineStr">
+        <is>
+          <t>Rationale: The word 'ඔයාට' is written as 'oyta' and 'කරන්නම්' is written as 'karannm' — both are abbreviated spelling variants.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="55" customHeight="1">
       <c r="A18" s="10" t="inlineStr">
         <is>
           <t>Neg_0017</t>
@@ -1132,8 +1302,18 @@
           <t>Fail</t>
         </is>
       </c>
-    </row>
-    <row r="19" ht="50" customHeight="1">
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>Isolated English Word Insertions in Singlish</t>
+        </is>
+      </c>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>Rationale: The single English word 'lunch' is inserted in between Singlish text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="55" customHeight="1">
       <c r="A19" s="12" t="inlineStr">
         <is>
           <t>Neg_0018</t>
@@ -1164,8 +1344,18 @@
           <t>Fail</t>
         </is>
       </c>
-    </row>
-    <row r="20" ht="50" customHeight="1">
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>Isolated English Word Insertions in Singlish</t>
+        </is>
+      </c>
+      <c r="H19" s="12" t="inlineStr">
+        <is>
+          <t>Rationale: Single English words 'office' and 'manager' are inserted in between Singlish text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="55" customHeight="1">
       <c r="A20" s="10" t="inlineStr">
         <is>
           <t>Neg_0019</t>
@@ -1196,8 +1386,18 @@
           <t>Fail</t>
         </is>
       </c>
-    </row>
-    <row r="21" ht="50" customHeight="1">
+      <c r="G20" s="10" t="inlineStr">
+        <is>
+          <t>Multi-Word English Phrases in Singlish</t>
+        </is>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>Rationale: The multi-word English phrase 'on the way' is inserted inside the Singlish input.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="55" customHeight="1">
       <c r="A21" s="12" t="inlineStr">
         <is>
           <t>Neg_0020</t>
@@ -1228,8 +1428,18 @@
           <t>Fail</t>
         </is>
       </c>
-    </row>
-    <row r="22" ht="50" customHeight="1">
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>Multi-Word English Phrases in Singlish</t>
+        </is>
+      </c>
+      <c r="H21" s="12" t="inlineStr">
+        <is>
+          <t>Rationale: The multi-word English phrase 'will be there shortly' is inserted at the start of the Singlish input.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="55" customHeight="1">
       <c r="A22" s="10" t="inlineStr">
         <is>
           <t>Neg_0021</t>
@@ -1260,8 +1470,18 @@
           <t>Fail</t>
         </is>
       </c>
-    </row>
-    <row r="23" ht="50" customHeight="1">
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>English Digital Terms in Singlish</t>
+        </is>
+      </c>
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>Rationale: Input includes digital terms 'WiFi' and 'password' inserted in the Singlish sentence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="55" customHeight="1">
       <c r="A23" s="12" t="inlineStr">
         <is>
           <t>Neg_0022</t>
@@ -1292,8 +1512,18 @@
           <t>Fail</t>
         </is>
       </c>
-    </row>
-    <row r="24" ht="50" customHeight="1">
+      <c r="G23" s="12" t="inlineStr">
+        <is>
+          <t>English Digital Terms in Singlish</t>
+        </is>
+      </c>
+      <c r="H23" s="12" t="inlineStr">
+        <is>
+          <t>Rationale: Input includes digital terms 'email' and 'check' inserted in the Singlish sentence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="55" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
           <t>Neg_0023</t>
@@ -1324,8 +1554,18 @@
           <t>Fail</t>
         </is>
       </c>
-    </row>
-    <row r="25" ht="50" customHeight="1">
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>Platform/App Names in Singlish</t>
+        </is>
+      </c>
+      <c r="H24" s="10" t="inlineStr">
+        <is>
+          <t>Rationale: Input includes the platform name 'Zoom' inserted in the Singlish sentence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="55" customHeight="1">
       <c r="A25" s="12" t="inlineStr">
         <is>
           <t>Neg_0024</t>
@@ -1356,8 +1596,18 @@
           <t>Fail</t>
         </is>
       </c>
-    </row>
-    <row r="26" ht="50" customHeight="1">
+      <c r="G25" s="12" t="inlineStr">
+        <is>
+          <t>Platform/App Names in Singlish</t>
+        </is>
+      </c>
+      <c r="H25" s="12" t="inlineStr">
+        <is>
+          <t>Rationale: Input includes the app name 'WhatsApp' inserted in the Singlish sentence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="55" customHeight="1">
       <c r="A26" s="10" t="inlineStr">
         <is>
           <t>Neg_0025</t>
@@ -1388,8 +1638,18 @@
           <t>Fail</t>
         </is>
       </c>
-    </row>
-    <row r="27" ht="50" customHeight="1">
+      <c r="G26" s="10" t="inlineStr">
+        <is>
+          <t>English Abbreviations/Acronyms in Singlish</t>
+        </is>
+      </c>
+      <c r="H26" s="10" t="inlineStr">
+        <is>
+          <t>Rationale: Input includes the acronym 'NIC' (National Identity Card) inserted in the Singlish sentence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="55" customHeight="1">
       <c r="A27" s="12" t="inlineStr">
         <is>
           <t>Neg_0026</t>
@@ -1420,8 +1680,18 @@
           <t>Fail</t>
         </is>
       </c>
-    </row>
-    <row r="28" ht="50" customHeight="1">
+      <c r="G27" s="12" t="inlineStr">
+        <is>
+          <t>English Abbreviations/Acronyms in Singlish</t>
+        </is>
+      </c>
+      <c r="H27" s="12" t="inlineStr">
+        <is>
+          <t>Rationale: Input includes the acronym 'ASAP' (As Soon As Possible) at the start of the Singlish sentence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="55" customHeight="1">
       <c r="A28" s="10" t="inlineStr">
         <is>
           <t>Neg_0027</t>
@@ -1452,8 +1722,18 @@
           <t>Fail</t>
         </is>
       </c>
-    </row>
-    <row r="29" ht="50" customHeight="1">
+      <c r="G28" s="10" t="inlineStr">
+        <is>
+          <t>English Clipped Forms in Singlish</t>
+        </is>
+      </c>
+      <c r="H28" s="10" t="inlineStr">
+        <is>
+          <t>Rationale: Input includes the clipped English word 'exam' inserted in the Singlish sentence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="55" customHeight="1">
       <c r="A29" s="12" t="inlineStr">
         <is>
           <t>Neg_0028</t>
@@ -1484,8 +1764,18 @@
           <t>Fail</t>
         </is>
       </c>
-    </row>
-    <row r="30" ht="50" customHeight="1">
+      <c r="G29" s="12" t="inlineStr">
+        <is>
+          <t>English Clipped Forms in Singlish</t>
+        </is>
+      </c>
+      <c r="H29" s="12" t="inlineStr">
+        <is>
+          <t>Rationale: Input includes clipped English words 'lab' and 'lecture' inserted in the Singlish sentence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="55" customHeight="1">
       <c r="A30" s="10" t="inlineStr">
         <is>
           <t>Neg_0029</t>
@@ -1516,8 +1806,18 @@
           <t>Fail</t>
         </is>
       </c>
-    </row>
-    <row r="31" ht="50" customHeight="1">
+      <c r="G30" s="10" t="inlineStr">
+        <is>
+          <t>Place Names Embedded in Singlish</t>
+        </is>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>Rationale: Input includes the place name 'Singapore' embedded inside the Singlish sentence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="55" customHeight="1">
       <c r="A31" s="12" t="inlineStr">
         <is>
           <t>Neg_0030</t>
@@ -1548,8 +1848,18 @@
           <t>Fail</t>
         </is>
       </c>
-    </row>
-    <row r="32" ht="50" customHeight="1">
+      <c r="G31" s="12" t="inlineStr">
+        <is>
+          <t>Place Names Embedded in Singlish</t>
+        </is>
+      </c>
+      <c r="H31" s="12" t="inlineStr">
+        <is>
+          <t>Rationale: Input includes the place name 'Colombo' embedded inside the Singlish sentence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="55" customHeight="1">
       <c r="A32" s="10" t="inlineStr">
         <is>
           <t>Neg_0031</t>
@@ -1580,8 +1890,18 @@
           <t>Fail</t>
         </is>
       </c>
-    </row>
-    <row r="33" ht="50" customHeight="1">
+      <c r="G32" s="10" t="inlineStr">
+        <is>
+          <t>Person Names Embedded in Singlish</t>
+        </is>
+      </c>
+      <c r="H32" s="10" t="inlineStr">
+        <is>
+          <t>Rationale: Input includes the person name 'Nimal' with honorific 'aiye' embedded in the Singlish sentence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="55" customHeight="1">
       <c r="A33" s="12" t="inlineStr">
         <is>
           <t>Neg_0032</t>
@@ -1612,8 +1932,18 @@
           <t>Fail</t>
         </is>
       </c>
-    </row>
-    <row r="34" ht="50" customHeight="1">
+      <c r="G33" s="12" t="inlineStr">
+        <is>
+          <t>Person Names Embedded in Singlish</t>
+        </is>
+      </c>
+      <c r="H33" s="12" t="inlineStr">
+        <is>
+          <t>Rationale: Input includes person names 'Sandya' and 'Kumara' embedded inside the Singlish sentence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="55" customHeight="1">
       <c r="A34" s="10" t="inlineStr">
         <is>
           <t>Neg_0033</t>
@@ -1644,8 +1974,18 @@
           <t>Fail</t>
         </is>
       </c>
-    </row>
-    <row r="35" ht="50" customHeight="1">
+      <c r="G34" s="10" t="inlineStr">
+        <is>
+          <t>Inputs with Numbers and Numeric Suffixes</t>
+        </is>
+      </c>
+      <c r="H34" s="10" t="inlineStr">
+        <is>
+          <t>Rationale: Input includes the ordinal number '1st' with a numeric suffix embedded in the Singlish sentence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="55" customHeight="1">
       <c r="A35" s="12" t="inlineStr">
         <is>
           <t>Neg_0034</t>
@@ -1676,8 +2016,18 @@
           <t>Fail</t>
         </is>
       </c>
-    </row>
-    <row r="36" ht="50" customHeight="1">
+      <c r="G35" s="12" t="inlineStr">
+        <is>
+          <t>Inputs with Numbers and Numeric Suffixes</t>
+        </is>
+      </c>
+      <c r="H35" s="12" t="inlineStr">
+        <is>
+          <t>Rationale: Input includes '100n' and '100yama' which are numbers with Singlish numeric suffixes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="55" customHeight="1">
       <c r="A36" s="10" t="inlineStr">
         <is>
           <t>Neg_0035</t>
@@ -1708,8 +2058,18 @@
           <t>Fail</t>
         </is>
       </c>
-    </row>
-    <row r="37" ht="50" customHeight="1">
+      <c r="G36" s="10" t="inlineStr">
+        <is>
+          <t>Inputs with Currency</t>
+        </is>
+      </c>
+      <c r="H36" s="10" t="inlineStr">
+        <is>
+          <t>Rationale: Input includes currency abbreviation 'Rs.' followed by the amount '2500' in the Singlish sentence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="55" customHeight="1">
       <c r="A37" s="12" t="inlineStr">
         <is>
           <t>Neg_0036</t>
@@ -1740,8 +2100,18 @@
           <t>Fail</t>
         </is>
       </c>
-    </row>
-    <row r="38" ht="50" customHeight="1">
+      <c r="G37" s="12" t="inlineStr">
+        <is>
+          <t>Inputs with Currency</t>
+        </is>
+      </c>
+      <c r="H37" s="12" t="inlineStr">
+        <is>
+          <t>Rationale: Input includes foreign currency code 'EUR' followed by the amount '3000' in the Singlish sentence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="55" customHeight="1">
       <c r="A38" s="10" t="inlineStr">
         <is>
           <t>Neg_0037</t>
@@ -1772,8 +2142,18 @@
           <t>Fail</t>
         </is>
       </c>
-    </row>
-    <row r="39" ht="50" customHeight="1">
+      <c r="G38" s="10" t="inlineStr">
+        <is>
+          <t>Inputs with Time Formats</t>
+        </is>
+      </c>
+      <c r="H38" s="10" t="inlineStr">
+        <is>
+          <t>Rationale: Input includes the time format '7:30PM' embedded in the Singlish sentence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="55" customHeight="1">
       <c r="A39" s="12" t="inlineStr">
         <is>
           <t>Neg_0038</t>
@@ -1804,8 +2184,18 @@
           <t>Fail</t>
         </is>
       </c>
-    </row>
-    <row r="40" ht="50" customHeight="1">
+      <c r="G39" s="12" t="inlineStr">
+        <is>
+          <t>Inputs with Time Formats</t>
+        </is>
+      </c>
+      <c r="H39" s="12" t="inlineStr">
+        <is>
+          <t>Rationale: Input includes the compound time format '12.00noon' embedded in the Singlish sentence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="55" customHeight="1">
       <c r="A40" s="10" t="inlineStr">
         <is>
           <t>Neg_0039</t>
@@ -1836,8 +2226,18 @@
           <t>Fail</t>
         </is>
       </c>
-    </row>
-    <row r="41" ht="50" customHeight="1">
+      <c r="G40" s="10" t="inlineStr">
+        <is>
+          <t>Inputs with Dates</t>
+        </is>
+      </c>
+      <c r="H40" s="10" t="inlineStr">
+        <is>
+          <t>Rationale: Input includes the ISO date format '2026-02-06' with a Singlish locative suffix 'ta' attached.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="55" customHeight="1">
       <c r="A41" s="12" t="inlineStr">
         <is>
           <t>Neg_0040</t>
@@ -1868,8 +2268,18 @@
           <t>Fail</t>
         </is>
       </c>
-    </row>
-    <row r="42" ht="50" customHeight="1">
+      <c r="G41" s="12" t="inlineStr">
+        <is>
+          <t>Inputs with Dates</t>
+        </is>
+      </c>
+      <c r="H41" s="12" t="inlineStr">
+        <is>
+          <t>Rationale: Input includes the date 'February 15' written in English embedded in the Singlish sentence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="55" customHeight="1">
       <c r="A42" s="10" t="inlineStr">
         <is>
           <t>Neg_0041</t>
@@ -1900,8 +2310,18 @@
           <t>Fail</t>
         </is>
       </c>
-    </row>
-    <row r="43" ht="50" customHeight="1">
+      <c r="G42" s="10" t="inlineStr">
+        <is>
+          <t>Inputs with Unit of Measurements</t>
+        </is>
+      </c>
+      <c r="H42" s="10" t="inlineStr">
+        <is>
+          <t>Rationale: Input includes the unit of measurement 'km' followed by '3k' (3 kilometres) in the Singlish sentence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="55" customHeight="1">
       <c r="A43" s="12" t="inlineStr">
         <is>
           <t>Neg_0042</t>
@@ -1932,8 +2352,18 @@
           <t>Fail</t>
         </is>
       </c>
-    </row>
-    <row r="44" ht="50" customHeight="1">
+      <c r="G43" s="12" t="inlineStr">
+        <is>
+          <t>Inputs with Unit of Measurements</t>
+        </is>
+      </c>
+      <c r="H43" s="12" t="inlineStr">
+        <is>
+          <t>Rationale: Input includes the unit 'adi' (feet) followed by '15k' as a numeric measurement in the Singlish sentence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="55" customHeight="1">
       <c r="A44" s="10" t="inlineStr">
         <is>
           <t>Neg_0043</t>
@@ -1964,8 +2394,18 @@
           <t>Fail</t>
         </is>
       </c>
-    </row>
-    <row r="45" ht="50" customHeight="1">
+      <c r="G44" s="10" t="inlineStr">
+        <is>
+          <t>Inputs with Slang and Casual Phrasing</t>
+        </is>
+      </c>
+      <c r="H44" s="10" t="inlineStr">
+        <is>
+          <t>Rationale: Input includes slang terms 'sirawata' and 'ela kiri' which are casual Singlish expressions meaning 'really cool'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="55" customHeight="1">
       <c r="A45" s="12" t="inlineStr">
         <is>
           <t>Neg_0044</t>
@@ -1996,8 +2436,18 @@
           <t>Fail</t>
         </is>
       </c>
-    </row>
-    <row r="46" ht="50" customHeight="1">
+      <c r="G45" s="12" t="inlineStr">
+        <is>
+          <t>Inputs with Slang and Casual Phrasing</t>
+        </is>
+      </c>
+      <c r="H45" s="12" t="inlineStr">
+        <is>
+          <t>Rationale: Input includes slang term 'machan' (friend) and casual expression 'adoo' used in informal Singlish conversation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="55" customHeight="1">
       <c r="A46" s="10" t="inlineStr">
         <is>
           <t>Neg_0045</t>
@@ -2028,8 +2478,18 @@
           <t>Fail</t>
         </is>
       </c>
-    </row>
-    <row r="47" ht="50" customHeight="1">
+      <c r="G46" s="10" t="inlineStr">
+        <is>
+          <t>Online Identifiers in Singlish</t>
+        </is>
+      </c>
+      <c r="H46" s="10" t="inlineStr">
+        <is>
+          <t>Evidence: Input includes the URL 'https://news.lk' as an online identifier embedded in the Singlish sentence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="55" customHeight="1">
       <c r="A47" s="12" t="inlineStr">
         <is>
           <t>Neg_0046</t>
@@ -2060,8 +2520,18 @@
           <t>Fail</t>
         </is>
       </c>
-    </row>
-    <row r="48" ht="50" customHeight="1">
+      <c r="G47" s="12" t="inlineStr">
+        <is>
+          <t>Online Identifiers in Singlish</t>
+        </is>
+      </c>
+      <c r="H47" s="12" t="inlineStr">
+        <is>
+          <t>Evidence: Input includes the email address 'amal234@gmail.com' as an online identifier embedded in the Singlish sentence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="55" customHeight="1">
       <c r="A48" s="10" t="inlineStr">
         <is>
           <t>Neg_0047</t>
@@ -2092,8 +2562,18 @@
           <t>Fail</t>
         </is>
       </c>
-    </row>
-    <row r="49" ht="50" customHeight="1">
+      <c r="G48" s="10" t="inlineStr">
+        <is>
+          <t>Inputs Containing Emojis</t>
+        </is>
+      </c>
+      <c r="H48" s="10" t="inlineStr">
+        <is>
+          <t>Rationale: Input contains the emoji 🥲 at the end of the Singlish sentence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="55" customHeight="1">
       <c r="A49" s="12" t="inlineStr">
         <is>
           <t>Neg_0048</t>
@@ -2124,8 +2604,18 @@
           <t>Fail</t>
         </is>
       </c>
-    </row>
-    <row r="50" ht="50" customHeight="1">
+      <c r="G49" s="12" t="inlineStr">
+        <is>
+          <t>Inputs Containing Emojis</t>
+        </is>
+      </c>
+      <c r="H49" s="12" t="inlineStr">
+        <is>
+          <t>Rationale: Input contains the emoji 😅 at the end of the Singlish sentence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="55" customHeight="1">
       <c r="A50" s="10" t="inlineStr">
         <is>
           <t>Neg_0049</t>
@@ -2156,8 +2646,18 @@
           <t>Fail</t>
         </is>
       </c>
-    </row>
-    <row r="51" ht="50" customHeight="1">
+      <c r="G50" s="10" t="inlineStr">
+        <is>
+          <t>Romanization / Spelling Variants</t>
+        </is>
+      </c>
+      <c r="H50" s="10" t="inlineStr">
+        <is>
+          <t>Rationale: Multiple consecutive spaces between words are used as an unconventional spacing variant in the Singlish input.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="55" customHeight="1">
       <c r="A51" s="12" t="inlineStr">
         <is>
           <t>Neg_0050</t>
@@ -2186,6 +2686,16 @@
       <c r="F51" s="13" t="inlineStr">
         <is>
           <t>Fail</t>
+        </is>
+      </c>
+      <c r="G51" s="12" t="inlineStr">
+        <is>
+          <t>Online Identifiers in Singlish</t>
+        </is>
+      </c>
+      <c r="H51" s="12" t="inlineStr">
+        <is>
+          <t>Evidence: Input includes '@Tharindu' as a social media mention identifier embedded in the Singlish sentence.</t>
         </is>
       </c>
     </row>
